--- a/output/pdf_financials_xlsx/GRN.xlsx
+++ b/output/pdf_financials_xlsx/GRN.xlsx
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">

--- a/output/pdf_financials_xlsx/GRN.xlsx
+++ b/output/pdf_financials_xlsx/GRN.xlsx
@@ -848,7 +848,7 @@
         <v>-0.193</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-5.053</v>
+        <v>-4.778</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-2.526</v>
@@ -876,7 +876,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.275</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.076</v>
@@ -997,10 +997,10 @@
         <v>-5.505</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-29.58</v>
+        <v>-28.526</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-1.863</v>
+        <v>-1.38</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-1.042</v>
@@ -1025,10 +1025,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-1.054</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-0.483</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>-0.193</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.053</v>
+        <v>-4.778</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.364</v>
@@ -1244,7 +1244,7 @@
         <v>-0.193</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.208</v>
+        <v>-3.933</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.364</v>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-46.12517812123205</v>
+        <v>-43.1108188096021</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-4.270925547867247</v>
@@ -1302,7 +1302,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.755546253662621</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-3.008709422011085</v>
@@ -1538,19 +1538,19 @@
         <v>0.576</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.742</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1566,19 +1566,19 @@
         <v>2.012</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>16.368</v>
+        <v>16.461</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>14.779</v>
+        <v>15.521</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>11.373</v>
+        <v>12.083</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8.787000000000001</v>
+        <v>9.022</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>9.509</v>
+        <v>10.072</v>
       </c>
     </row>
     <row r="42">
@@ -1762,19 +1762,19 @@
         <v>1.745</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.462</v>
+        <v>12.369</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>15.735</v>
+        <v>14.993</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>16.144</v>
+        <v>15.434</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.068</v>
+        <v>6.833</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.132</v>
+        <v>3.569</v>
       </c>
     </row>
     <row r="49">
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.978</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -2309,22 +2309,22 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.787</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>3.537</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>3.573</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>2.987</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.569</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>4.345</v>
       </c>
     </row>
     <row r="68">
@@ -3213,10 +3213,10 @@
         <v>-5.505</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-29.58</v>
+        <v>-28.526</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-1.863</v>
+        <v>-1.38</v>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002142</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -8798,7 +8798,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -9317,7 +9321,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -10893,7 +10901,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -11515,7 +11527,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -12023,7 +12039,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>0.571</v>
       </c>
@@ -12447,7 +12467,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="n">
         <v>-0.002142</v>
       </c>
@@ -13933,7 +13957,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -13980,7 +14008,11 @@
           <t>Net loss from discontinued operations (note 5)</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -16333,7 +16365,11 @@
           <t>Income tax recovery (note 23)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
